--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2012-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2012-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAF60F2B-2828-4DED-80EA-C849859620ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17A1F57C-53FD-4533-8957-96C9D8009FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2D6E5EBC-3BA7-4157-B6DB-1028ECE65783}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{80FE9846-2E48-452F-9E39-E4C4D890E82E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1526,25 +1526,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5ACA28-DEE8-4CC6-9F7E-CF08654F0058}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B44C027-66D3-4EDB-9852-3C15A1D3EEB3}">
   <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1698,7 +1698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="41">
         <v>2023</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2022</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
         <v>26</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="22" t="s">
         <v>39</v>
@@ -2494,7 +2494,7 @@
       <c r="Q19" s="48"/>
       <c r="R19" s="48"/>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2021</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2020</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>2019</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2018</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <v>2017</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2016</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2015</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2014</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2013</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2012</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>2011</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2010</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>2009</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2008</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="41">
         <v>2007</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2006</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="41">
         <v>2005</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2004</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="41">
         <v>2003</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2002</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="41">
         <v>2001</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2000</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="41">
         <v>1999</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1998</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="41">
         <v>1997</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1996</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="41">
         <v>1995</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1994</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="41">
         <v>1993</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1992</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="41">
         <v>1991</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>1990</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="41">
         <v>1989</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <v>1988</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="41">
         <v>1986</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <v>1985</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
         <v>48</v>
       </c>
